--- a/InLaLi2program.xlsx
+++ b/InLaLi2program.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ian/Documents/GitHub/inlali2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DE6C0D-A233-6242-895A-7895513425F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FB8951-6AA3-B74F-AE84-8C45C14CF68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{9775C8A0-C775-C643-8A3E-712D908CC006}"/>
   </bookViews>
@@ -177,10 +177,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NOMOTO Hiroki Nomoto; Gede Primahadi WIJAYA RAJEG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Refleksi bunyi Proto-Austronesia pada Bahasa Jawa dialek Ngapak di Banyumas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -274,6 +270,10 @@
   </si>
   <si>
     <t>Ratu Boko</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOMOTO Hiroki; Gede Primahadi WIJAYA RAJEG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -721,7 +721,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -797,7 +797,7 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>33</v>
@@ -814,10 +814,10 @@
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -842,10 +842,10 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -859,10 +859,10 @@
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -876,10 +876,10 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -896,7 +896,7 @@
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -910,10 +910,10 @@
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -938,10 +938,10 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" t="s">
         <v>41</v>
-      </c>
-      <c r="E17" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -972,10 +972,10 @@
         <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -989,10 +989,10 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1068,7 +1068,7 @@
         <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1110,10 +1110,10 @@
         <v>19</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1135,10 +1135,10 @@
         <v>0.5625</v>
       </c>
       <c r="C30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1149,10 +1149,10 @@
         <v>0.375</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/InLaLi2program.xlsx
+++ b/InLaLi2program.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ian/Documents/GitHub/inlali2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FB8951-6AA3-B74F-AE84-8C45C14CF68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8D67E6-9B35-2B4E-B6D0-CB4B2AA2A159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{9775C8A0-C775-C643-8A3E-712D908CC006}"/>
   </bookViews>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TBA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EKARINA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -274,6 +270,10 @@
   </si>
   <si>
     <t>NOMOTO Hiroki; Gede Primahadi WIJAYA RAJEG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bahasa dan Budaya Jawa di Gereja Katolik: Pemertahanan dan Identitas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -687,7 +687,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0.375</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -715,13 +715,13 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -732,13 +732,13 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -749,7 +749,7 @@
         <v>0.5</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -760,13 +760,13 @@
         <v>0.5625</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
         <v>17</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -777,13 +777,13 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -794,13 +794,13 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -811,13 +811,13 @@
         <v>0.625</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -828,7 +828,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -839,13 +839,13 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -856,13 +856,13 @@
         <v>0.6875</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -873,13 +873,13 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -890,13 +890,13 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -907,13 +907,13 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -924,7 +924,7 @@
         <v>0.5</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -935,13 +935,13 @@
         <v>0.5625</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
         <v>40</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -952,13 +952,13 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" t="s">
         <v>31</v>
-      </c>
-      <c r="E18" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -969,13 +969,13 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -986,13 +986,13 @@
         <v>0.625</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1011,13 +1011,13 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1028,13 +1028,13 @@
         <v>0.6875</v>
       </c>
       <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
         <v>23</v>
-      </c>
-      <c r="D23" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1045,13 +1045,13 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s">
         <v>27</v>
-      </c>
-      <c r="E24" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1062,13 +1062,13 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1079,7 +1079,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1090,13 +1090,13 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="C27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" t="s">
         <v>19</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>20</v>
-      </c>
-      <c r="E27" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1107,13 +1107,13 @@
         <v>0.5</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1124,7 +1124,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1135,10 +1135,10 @@
         <v>0.5625</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1149,10 +1149,10 @@
         <v>0.375</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/InLaLi2program.xlsx
+++ b/InLaLi2program.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ian/Documents/GitHub/inlali2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/85abc6e525293a5a/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8D67E6-9B35-2B4E-B6D0-CB4B2AA2A159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{4419AF60-83BC-9140-8368-EAFBE46C2476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4D72009-404E-A245-9ECF-738F4D4CCCE9}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{9775C8A0-C775-C643-8A3E-712D908CC006}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
   <si>
     <t>Authors</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -105,14 +105,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Yusuf Willem SAWAKI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>One word, many functions: The iamative suda `already' and its polyfunctionality in Papuan Malay</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Sociolinguistics</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -133,10 +125,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Parit as linguistic-ecological memoryscape: Toponymy, oral history, and urban transformation in Pontianak</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Muhammad SYAIFULLOH; Adisti Primi WULAN; Karel JUNIARDI; Agus DEDIANSYAH</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -213,10 +201,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Arina ISTI'ANAH; Emi NURSANTI, Nadia KHUMAIRO MA'SHUMAH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Field trip</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -274,6 +258,28 @@
   </si>
   <si>
     <t>Bahasa dan Budaya Jawa di Gereja Katolik: Pemertahanan dan Identitas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parit as linguistic-ecological memoryscape: Toponymy, oral history, and urban transformation in Pontianak [Online]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Opening</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arina ISTI'ANAH; Emi NURSANTI; Nadia KHUMAIRO MA'SHUMAH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\makecell[lt]{1. Welcoming speech from the committee\\
+2. Welcoming speech from the Dean\\
+3. Cultural performance}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -323,7 +329,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -335,6 +341,9 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -670,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4033F1CB-EF2A-B54C-9B64-8C662E7A4084}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -701,27 +710,24 @@
         <v>46246</v>
       </c>
       <c r="B2" s="3">
-        <v>0.375</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="57">
       <c r="A3" s="1">
         <v>46246</v>
       </c>
       <c r="B3" s="3">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" t="s">
-        <v>51</v>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -729,16 +735,16 @@
         <v>46246</v>
       </c>
       <c r="B4" s="3">
-        <v>0.45833333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -746,10 +752,10 @@
         <v>46246</v>
       </c>
       <c r="B5" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -757,16 +763,16 @@
         <v>46246</v>
       </c>
       <c r="B6" s="3">
-        <v>0.5625</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -774,16 +780,10 @@
         <v>46246</v>
       </c>
       <c r="B7" s="3">
-        <v>0.58333333333333337</v>
+        <v>0.46875</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -791,16 +791,16 @@
         <v>46246</v>
       </c>
       <c r="B8" s="3">
-        <v>0.60416666666666663</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -808,16 +808,16 @@
         <v>46246</v>
       </c>
       <c r="B9" s="3">
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -825,10 +825,16 @@
         <v>46246</v>
       </c>
       <c r="B10" s="3">
-        <v>0.64583333333333337</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -836,16 +842,10 @@
         <v>46246</v>
       </c>
       <c r="B11" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -853,16 +853,16 @@
         <v>46246</v>
       </c>
       <c r="B12" s="3">
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -870,50 +870,44 @@
         <v>46246</v>
       </c>
       <c r="B13" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B14" s="3">
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B15" s="3">
-        <v>0.45833333333333331</v>
+        <v>0.6875</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -921,10 +915,16 @@
         <v>46247</v>
       </c>
       <c r="B16" s="3">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -932,16 +932,10 @@
         <v>46247</v>
       </c>
       <c r="B17" s="3">
-        <v>0.5625</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -949,16 +943,16 @@
         <v>46247</v>
       </c>
       <c r="B18" s="3">
-        <v>0.58333333333333337</v>
+        <v>0.4375</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -966,16 +960,10 @@
         <v>46247</v>
       </c>
       <c r="B19" s="3">
-        <v>0.60416666666666663</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -983,16 +971,16 @@
         <v>46247</v>
       </c>
       <c r="B20" s="3">
-        <v>0.625</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1000,7 +988,16 @@
         <v>46247</v>
       </c>
       <c r="B21" s="3">
-        <v>0.64583333333333337</v>
+        <v>0.5625</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1008,16 +1005,16 @@
         <v>46247</v>
       </c>
       <c r="B22" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E22" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1025,16 +1022,16 @@
         <v>46247</v>
       </c>
       <c r="B23" s="3">
-        <v>0.6875</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E23" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1042,61 +1039,61 @@
         <v>46247</v>
       </c>
       <c r="B24" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B25" s="3">
-        <v>0.41666666666666669</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="C25" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B26" s="3">
-        <v>0.45833333333333331</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B27" s="3">
-        <v>0.47916666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E27" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1104,13 +1101,13 @@
         <v>46248</v>
       </c>
       <c r="B28" s="3">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
         <v>42</v>
@@ -1121,10 +1118,10 @@
         <v>46248</v>
       </c>
       <c r="B29" s="3">
-        <v>0.52083333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="C29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1132,27 +1129,72 @@
         <v>46248</v>
       </c>
       <c r="B30" s="3">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>17</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B31" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B32" s="3">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B33" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C33" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1">
         <v>46249</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B34" s="3">
         <v>0.375</v>
       </c>
-      <c r="C31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" t="s">
-        <v>47</v>
+      <c r="C34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/InLaLi2program.xlsx
+++ b/InLaLi2program.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/85abc6e525293a5a/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ian/Documents/GitHub/inlali2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{4419AF60-83BC-9140-8368-EAFBE46C2476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4D72009-404E-A245-9ECF-738F4D4CCCE9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C783CA8D-D819-D647-B492-84A3584DE2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{9775C8A0-C775-C643-8A3E-712D908CC006}"/>
   </bookViews>
@@ -165,10 +165,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Dyah SUSILAWATI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Discursive constructions of (natural) disasters in Southeast Asian newspapers: A corpus-assisted discourse study</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -277,9 +273,13 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>\makecell[lt]{1. Welcoming speech from the committee\\
-2. Welcoming speech from the Dean\\
-3. Cultural performance}</t>
+    <t>Dyah SUSILAWATI; Umi SA'DIYAH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Welcoming speech from the committee&lt;br&gt;
+2. Welcoming speech from the Dean&lt;br&gt;
+3. Cultural performance</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -724,7 +724,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>59</v>
@@ -744,7 +744,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -772,7 +772,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -814,7 +814,7 @@
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
         <v>29</v>
@@ -831,10 +831,10 @@
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -859,10 +859,10 @@
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -876,10 +876,10 @@
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -893,10 +893,10 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -907,7 +907,7 @@
         <v>0.6875</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -924,7 +924,7 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -949,10 +949,10 @@
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -977,10 +977,10 @@
         <v>14</v>
       </c>
       <c r="D20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" t="s">
         <v>36</v>
-      </c>
-      <c r="E20" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1011,7 +1011,7 @@
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
         <v>30</v>
@@ -1028,10 +1028,10 @@
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1076,7 +1076,7 @@
         <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1152,10 +1152,10 @@
         <v>16</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1177,10 +1177,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1191,10 +1191,10 @@
         <v>0.375</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/InLaLi2program.xlsx
+++ b/InLaLi2program.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ian/Documents/GitHub/inlali2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C783CA8D-D819-D647-B492-84A3584DE2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B189D367-B9E4-8A4A-B32C-42FC44F896EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{9775C8A0-C775-C643-8A3E-712D908CC006}"/>
   </bookViews>
@@ -921,10 +921,10 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -949,10 +949,10 @@
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:5">
